--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484154_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484154_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. LLABRES TUGORES</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.4038</v>
+        <v>3.5992</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9349</v>
+        <v>5.5402</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.5311</v>
+        <v>-1.9409</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6445</v>
+        <v>1.8865</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1613</v>
+        <v>3.5784</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8058</v>
+        <v>-1.6919</v>
       </c>
       <c r="J2" t="n">
-        <v>0.408</v>
+        <v>4.0571</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2876</v>
+        <v>3.8965</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1205</v>
+        <v>0.1606</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0525</v>
+        <v>-2.1707</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.1263</v>
+        <v>-0.3181</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.9263</v>
+        <v>-1.8525</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3968</v>
+        <v>1.9838</v>
       </c>
       <c r="S2" t="n">
-        <v>4.437</v>
+        <v>1.1095</v>
       </c>
       <c r="T2" t="n">
-        <v>2.8399</v>
+        <v>0.788</v>
       </c>
       <c r="U2" t="n">
-        <v>1.5972</v>
+        <v>0.3216</v>
       </c>
       <c r="V2" t="n">
-        <v>1.2065</v>
+        <v>0.6032</v>
       </c>
       <c r="W2" t="n">
         <v>2.6789</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.4724</v>
+        <v>-2.0757</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>T. LLOBERA BIBILONI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6874</v>
+        <v>2.849</v>
       </c>
       <c r="E3" t="n">
-        <v>5.3758</v>
+        <v>3.2847</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6884</v>
+        <v>-0.4357</v>
       </c>
       <c r="G3" t="n">
-        <v>1.8865</v>
+        <v>1.7917</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5784</v>
+        <v>2.1622</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.6919</v>
+        <v>-0.3705</v>
       </c>
       <c r="J3" t="n">
-        <v>4.0571</v>
+        <v>3.8967</v>
       </c>
       <c r="K3" t="n">
-        <v>3.8965</v>
+        <v>2.6868</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1606</v>
+        <v>1.21</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.1707</v>
+        <v>-2.1051</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.3181</v>
+        <v>-0.5246</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.8525</v>
+        <v>-1.5805</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>0.7935</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9838</v>
+        <v>1.7855</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1977</v>
+        <v>0.6504</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6236</v>
+        <v>0.3799</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5741000000000001</v>
+        <v>0.2706</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6032</v>
+        <v>-0.3866</v>
       </c>
       <c r="W3" t="n">
-        <v>2.6789</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.0757</v>
+        <v>-0.3866</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. LLOBERA BIBILONI</t>
+          <t>P. LLABRES TUGORES</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1425</v>
+        <v>2.1604</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7745</v>
+        <v>3.3648</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6321</v>
+        <v>-1.2044</v>
       </c>
       <c r="G4" t="n">
-        <v>1.7917</v>
+        <v>-0.6445</v>
       </c>
       <c r="H4" t="n">
-        <v>2.1622</v>
+        <v>0.1613</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.3705</v>
+        <v>-0.8058</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8967</v>
+        <v>0.408</v>
       </c>
       <c r="K4" t="n">
-        <v>2.6868</v>
+        <v>0.2876</v>
       </c>
       <c r="L4" t="n">
-        <v>1.21</v>
+        <v>0.1205</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1051</v>
+        <v>-1.0525</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.5246</v>
+        <v>-0.1263</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.5805</v>
+        <v>-0.9263</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7935</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0561</v>
+        <v>2.1936</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1303</v>
+        <v>1.2697</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0742</v>
+        <v>0.9238</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3866</v>
+        <v>1.2065</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.6789</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.3866</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0435</v>
+        <v>1.9666</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5687</v>
+        <v>1.1833</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4747</v>
+        <v>0.7834</v>
       </c>
       <c r="G5" t="n">
         <v>0.8255</v>
@@ -844,13 +844,13 @@
         <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2034</v>
+        <v>1.1266</v>
       </c>
       <c r="T5" t="n">
-        <v>1.3661</v>
+        <v>0.9807</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1627</v>
+        <v>0.1459</v>
       </c>
       <c r="V5" t="n">
         <v>0.4113</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. OCHOGAVIA CIFRE</t>
+          <t>L. SANCHEZ MORENO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0883</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3942</v>
+        <v>3.2046</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3059</v>
+        <v>-2.3654</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5306</v>
+        <v>1.4338</v>
       </c>
       <c r="H6" t="n">
-        <v>2.742</v>
+        <v>0.4739</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2113</v>
+        <v>0.9599</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5079</v>
+        <v>3.6636</v>
       </c>
       <c r="K6" t="n">
-        <v>2.8682</v>
+        <v>0.7216</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3604</v>
+        <v>2.942</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0228</v>
+        <v>-2.2297</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1263</v>
+        <v>-0.2477</v>
       </c>
       <c r="O6" t="n">
-        <v>0.149</v>
+        <v>-1.9821</v>
       </c>
       <c r="P6" t="n">
+        <v>0.9919</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-0.9919</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-1.9838</v>
-      </c>
       <c r="R6" t="n">
-        <v>0.9919</v>
+        <v>1.9838</v>
       </c>
       <c r="S6" t="n">
-        <v>1.756</v>
+        <v>1.213</v>
       </c>
       <c r="T6" t="n">
-        <v>1.6042</v>
+        <v>0.5329</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1519</v>
+        <v>0.68</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2065</v>
+        <v>-2.7996</v>
       </c>
       <c r="W6" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.4724</v>
+        <v>-2.7996</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. SANCHEZ MORENO</t>
+          <t>P. FLUXA PAYERAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2871</v>
+        <v>0.2843</v>
       </c>
       <c r="E7" t="n">
-        <v>2.428</v>
+        <v>-0.5603</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.1409</v>
+        <v>0.8446</v>
       </c>
       <c r="G7" t="n">
-        <v>1.4338</v>
+        <v>-1.9084</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4739</v>
+        <v>-0.5947</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9599</v>
+        <v>-1.3137</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6636</v>
+        <v>-1.9198</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7216</v>
+        <v>-0.5995</v>
       </c>
       <c r="L7" t="n">
-        <v>2.942</v>
+        <v>-1.3202</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.2297</v>
+        <v>0.0114</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2477</v>
+        <v>0.0049</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.9821</v>
+        <v>0.0065</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9919</v>
+        <v>0.7935</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9838</v>
+        <v>0.7935</v>
       </c>
       <c r="S7" t="n">
-        <v>0.6609</v>
+        <v>0.1927</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2436</v>
+        <v>0.1531</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9045</v>
+        <v>0.0396</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.7996</v>
+        <v>1.2065</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2065</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.7996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. FLUXA PAYERAS</t>
+          <t>M. OCHOGAVIA CIFRE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0803</v>
+        <v>0.2363</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7643</v>
+        <v>0.3739</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8446</v>
+        <v>-0.1375</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.9084</v>
+        <v>1.5306</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5947</v>
+        <v>2.742</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3137</v>
+        <v>-1.2113</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.9198</v>
+        <v>1.5079</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5995</v>
+        <v>2.8682</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.3202</v>
+        <v>-1.3604</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0114</v>
+        <v>0.0228</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0049</v>
+        <v>-0.1263</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0065</v>
+        <v>0.149</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7935</v>
+        <v>-0.9919</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9838</v>
       </c>
       <c r="R8" t="n">
-        <v>0.7935</v>
+        <v>0.9919</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0113</v>
+        <v>0.9041</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.051</v>
+        <v>0.5839</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0396</v>
+        <v>0.3202</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2065</v>
+        <v>-1.2065</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3452</v>
+        <v>-1.1131</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2057</v>
+        <v>-0.0016</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1395</v>
+        <v>-1.1115</v>
       </c>
       <c r="G9" t="n">
         <v>-3.3283</v>
@@ -1156,13 +1156,13 @@
         <v>0.3968</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5004999999999999</v>
+        <v>0.7326</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0056</v>
+        <v>0.1985</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5061</v>
+        <v>0.5342</v>
       </c>
       <c r="V9" t="n">
         <v>1.0858</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.9286</v>
+        <v>-2.8561</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.2513</v>
+        <v>-2.2909</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6773</v>
+        <v>-0.5651</v>
       </c>
       <c r="G10" t="n">
         <v>-4.3752</v>
@@ -1234,13 +1234,13 @@
         <v>0.3968</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0498</v>
+        <v>1.1223</v>
       </c>
       <c r="T10" t="n">
-        <v>0.7993</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0.2505</v>
+        <v>0.3627</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.8972</v>
+        <v>-2.9537</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.4788</v>
+        <v>-0.8439</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.4184</v>
+        <v>-2.1098</v>
       </c>
       <c r="G11" t="n">
         <v>-1.2296</v>
@@ -1312,13 +1312,13 @@
         <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>0.9313</v>
+        <v>1.8748</v>
       </c>
       <c r="T11" t="n">
-        <v>0.6859</v>
+        <v>1.3208</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2454</v>
+        <v>0.554</v>
       </c>
       <c r="V11" t="n">
         <v>-1.615</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8812</v>
+        <v>-4.7082</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2523</v>
+        <v>-3.1073</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.629</v>
+        <v>-1.6009</v>
       </c>
       <c r="G12" t="n">
         <v>-5.7679</v>
@@ -1390,13 +1390,13 @@
         <v>0.5952</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5878</v>
+        <v>0.5852000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.9975000000000001</v>
+        <v>0.1475</v>
       </c>
       <c r="U12" t="n">
-        <v>0.4097</v>
+        <v>0.4378</v>
       </c>
       <c r="V12" t="n">
         <v>-0.1206</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3192999999999984</v>
+        <v>0.3039000000000005</v>
       </c>
       <c r="E13" t="n">
-        <v>9.5237</v>
+        <v>10.1475</v>
       </c>
       <c r="F13" t="n">
-        <v>-9.843299999999999</v>
+        <v>-9.8432</v>
       </c>
       <c r="G13" t="n">
         <v>-9.785800000000002</v>
@@ -1444,10 +1444,10 @@
         <v>5.9779</v>
       </c>
       <c r="K13" t="n">
-        <v>9.606400000000001</v>
+        <v>9.606399999999997</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.628499999999999</v>
+        <v>-3.6285</v>
       </c>
       <c r="M13" t="n">
         <v>-15.7637</v>
@@ -1468,13 +1468,13 @@
         <v>11.9031</v>
       </c>
       <c r="S13" t="n">
-        <v>11.0814</v>
+        <v>11.7048</v>
       </c>
       <c r="T13" t="n">
-        <v>6.491</v>
+        <v>7.114599999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>4.5905</v>
+        <v>4.590400000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-1.615</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.843</v>
+        <v>5.2928</v>
       </c>
       <c r="E14" t="n">
-        <v>4.2786</v>
+        <v>4.7887</v>
       </c>
       <c r="F14" t="n">
-        <v>0.5644</v>
+        <v>0.504</v>
       </c>
       <c r="G14" t="n">
         <v>5.0485</v>
@@ -1546,13 +1546,13 @@
         <v>1.5871</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0072</v>
+        <v>-1.5574</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.1846</v>
+        <v>-0.6744</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8226</v>
+        <v>-0.883</v>
       </c>
       <c r="V14" t="n">
         <v>1.2065</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.0812</v>
+        <v>2.1756</v>
       </c>
       <c r="E15" t="n">
-        <v>2.6007</v>
+        <v>2.4987</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5195</v>
+        <v>-0.3231</v>
       </c>
       <c r="G15" t="n">
         <v>1.9119</v>
@@ -1624,13 +1624,13 @@
         <v>1.9838</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.9776</v>
+        <v>-1.8832</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7537</v>
+        <v>-0.8558</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2239</v>
+        <v>-1.0275</v>
       </c>
       <c r="V15" t="n">
         <v>2.1469</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1644</v>
+        <v>1.3642</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5253</v>
+        <v>4.7293</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.3609</v>
+        <v>-3.3652</v>
       </c>
       <c r="G16" t="n">
         <v>5.1775</v>
@@ -1702,13 +1702,13 @@
         <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.811</v>
+        <v>-1.6112</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8161</v>
+        <v>-0.612</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9949</v>
+        <v>-0.9992</v>
       </c>
       <c r="V16" t="n">
         <v>-1.0118</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>L. NDIAYE</t>
+          <t>J. MESADO PLANELLS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9301</v>
+        <v>0.2198</v>
       </c>
       <c r="E17" t="n">
-        <v>0.7257</v>
+        <v>0.1202</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2044</v>
+        <v>0.09959999999999999</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.9407</v>
+        <v>0.8967000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.2193</v>
+        <v>0.3124</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2786</v>
+        <v>0.5843</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.093</v>
+        <v>0.0805</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.093</v>
+        <v>0.0403</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.0402</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1523</v>
+        <v>0.8162</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1263</v>
+        <v>0.2721</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2786</v>
+        <v>0.5442</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5952</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3968</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2595</v>
+        <v>-0.411</v>
       </c>
       <c r="T17" t="n">
-        <v>1.6042</v>
+        <v>0.0397</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3447</v>
+        <v>-0.4506</v>
       </c>
       <c r="V17" t="n">
-        <v>1.2065</v>
+        <v>-0.266</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. MESADO PLANELLS</t>
+          <t>D. COFFIE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0616</v>
+        <v>0.1724</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0181</v>
+        <v>1.1685</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0435</v>
+        <v>-0.9961</v>
       </c>
       <c r="G18" t="n">
-        <v>0.8967000000000001</v>
+        <v>0.6016</v>
       </c>
       <c r="H18" t="n">
-        <v>0.3124</v>
+        <v>-1.6734</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5843</v>
+        <v>2.2751</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0805</v>
+        <v>2.4118</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0403</v>
+        <v>0.3183</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0402</v>
+        <v>2.0935</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8162</v>
+        <v>-1.8102</v>
       </c>
       <c r="N18" t="n">
-        <v>0.2721</v>
+        <v>-1.9917</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5442</v>
+        <v>0.1815</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-0.7935</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>2.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5691000000000001</v>
+        <v>-1.7827</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.0623</v>
+        <v>-0.9465</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5067</v>
+        <v>-0.8362000000000001</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.266</v>
+        <v>2.1469</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.6789</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.266</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. CASTILLO EDIO</t>
+          <t>L. NDIAYE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.3454</v>
+        <v>-0.182</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0165</v>
+        <v>-0.4986</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3289</v>
+        <v>0.3166</v>
       </c>
       <c r="G19" t="n">
-        <v>1.0931</v>
+        <v>-0.9407</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.2402</v>
+        <v>-1.2193</v>
       </c>
       <c r="I19" t="n">
-        <v>2.3333</v>
+        <v>0.2786</v>
       </c>
       <c r="J19" t="n">
-        <v>2.4296</v>
+        <v>-1.093</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4138</v>
+        <v>-1.093</v>
       </c>
       <c r="L19" t="n">
-        <v>2.0157</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3365</v>
+        <v>0.1523</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.6541</v>
+        <v>-0.1263</v>
       </c>
       <c r="O19" t="n">
-        <v>0.3176</v>
+        <v>0.2786</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R19" t="n">
-        <v>1.9838</v>
+        <v>0.3968</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.0417</v>
+        <v>0.1474</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0655</v>
+        <v>0.3798</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.9762</v>
+        <v>-0.2324</v>
       </c>
       <c r="V19" t="n">
-        <v>0.6032</v>
+        <v>1.2065</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6032</v>
+        <v>1.2065</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. COFFIE</t>
+          <t>A. CASTILLO EDIO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.7441</v>
+        <v>-0.2196</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5563</v>
+        <v>0.08550000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3005</v>
+        <v>-0.3051</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6016</v>
+        <v>1.0931</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.6734</v>
+        <v>-1.2402</v>
       </c>
       <c r="I20" t="n">
-        <v>2.2751</v>
+        <v>2.3333</v>
       </c>
       <c r="J20" t="n">
-        <v>2.4118</v>
+        <v>2.4296</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3183</v>
+        <v>0.4138</v>
       </c>
       <c r="L20" t="n">
-        <v>2.0935</v>
+        <v>2.0157</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8102</v>
+        <v>-1.3365</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.9917</v>
+        <v>-1.6541</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1815</v>
+        <v>0.3176</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.7935</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.9758</v>
+        <v>-1.9838</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1822</v>
+        <v>1.9838</v>
       </c>
       <c r="S20" t="n">
-        <v>-2.6992</v>
+        <v>-1.9159</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.5586</v>
+        <v>-0.9634</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1406</v>
+        <v>-0.9524</v>
       </c>
       <c r="V20" t="n">
-        <v>2.1469</v>
+        <v>0.6032</v>
       </c>
       <c r="W20" t="n">
-        <v>2.6789</v>
+        <v>0.6032</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8375</v>
+        <v>-0.9217</v>
       </c>
       <c r="E21" t="n">
         <v>-0.3539</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4836</v>
+        <v>-0.5678</v>
       </c>
       <c r="G21" t="n">
         <v>0.2267</v>
@@ -2092,13 +2092,13 @@
         <v>0.3968</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2545</v>
+        <v>-0.3387</v>
       </c>
       <c r="T21" t="n">
         <v>-0.3741</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1196</v>
+        <v>0.0354</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2065</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.9659</v>
+        <v>-1.0781</v>
       </c>
       <c r="E22" t="n">
         <v>-0.8069</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.159</v>
+        <v>-0.2712</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4838</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0499</v>
+        <v>-0.0623</v>
       </c>
       <c r="T22" t="n">
         <v>-0.187</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2369</v>
+        <v>0.1247</v>
       </c>
       <c r="V22" t="n">
         <v>-0.532</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.868</v>
+        <v>-5.8238</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6842</v>
+        <v>-1.8883</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.1837</v>
+        <v>-3.9355</v>
       </c>
       <c r="G23" t="n">
         <v>-3.7457</v>
@@ -2248,13 +2248,13 @@
         <v>1.5871</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0304</v>
+        <v>-0.9862</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1926</v>
+        <v>-0.3967</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8378</v>
+        <v>-0.5896</v>
       </c>
       <c r="V23" t="n">
         <v>-2.6789</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.3193999999999981</v>
+        <v>0.9996</v>
       </c>
       <c r="E24" t="n">
-        <v>9.843199999999998</v>
+        <v>9.8432</v>
       </c>
       <c r="F24" t="n">
-        <v>-9.5238</v>
+        <v>-8.843800000000002</v>
       </c>
       <c r="G24" t="n">
-        <v>9.7858</v>
+        <v>9.785800000000002</v>
       </c>
       <c r="H24" t="n">
-        <v>-6.376300000000001</v>
+        <v>-6.3763</v>
       </c>
       <c r="I24" t="n">
         <v>16.1622</v>
@@ -2326,13 +2326,13 @@
         <v>11.9031</v>
       </c>
       <c r="S24" t="n">
-        <v>-11.0813</v>
+        <v>-10.4012</v>
       </c>
       <c r="T24" t="n">
-        <v>-4.5903</v>
+        <v>-4.590400000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-6.490899999999999</v>
+        <v>-5.8108</v>
       </c>
       <c r="V24" t="n">
         <v>1.614799999999999</v>
